--- a/data/trans_orig/IP15-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP15-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7523</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16706</t>
+          <t>16944</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>7701</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17879</t>
+          <t>17941</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17543</t>
+          <t>17736</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31524</t>
+          <t>32432</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35862</t>
+          <t>35624</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45045</t>
+          <t>45115</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42338</t>
+          <t>42276</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52468</t>
+          <t>52516</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>81261</t>
+          <t>80353</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95242</t>
+          <t>95049</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,27%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11484</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23005</t>
+          <t>23193</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13372</t>
+          <t>13770</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26826</t>
+          <t>27094</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28691</t>
+          <t>28854</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45760</t>
+          <t>46844</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>78557</t>
+          <t>78369</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90078</t>
+          <t>90304</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>81931</t>
+          <t>81663</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95385</t>
+          <t>94987</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164559</t>
+          <t>163475</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181628</t>
+          <t>181465</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,28%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17443</t>
+          <t>18287</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>16142</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16083</t>
+          <t>15582</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29664</t>
+          <t>29690</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>50154</t>
+          <t>49310</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60303</t>
+          <t>60413</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54693</t>
+          <t>54185</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63515</t>
+          <t>64048</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108260</t>
+          <t>108234</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>121841</t>
+          <t>122342</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,7%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>10579</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22414</t>
+          <t>22668</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11021</t>
+          <t>10954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22918</t>
+          <t>22656</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24678</t>
+          <t>25800</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42370</t>
+          <t>40962</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52447</t>
+          <t>52193</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63673</t>
+          <t>64282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56193</t>
+          <t>56455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>68090</t>
+          <t>68157</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>111602</t>
+          <t>113010</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>129294</t>
+          <t>128172</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,24%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5367</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14396</t>
+          <t>13718</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13050</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11663</t>
+          <t>11228</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23805</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27456</t>
+          <t>28134</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36485</t>
+          <t>36838</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>31793</t>
+          <t>32408</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40671</t>
+          <t>40796</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>62890</t>
+          <t>62974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75032</t>
+          <t>75467</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>87,05%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17928</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15899</t>
+          <t>15913</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>16654</t>
+          <t>16826</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30660</t>
+          <t>30242</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,12%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>38127</t>
+          <t>38281</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48422</t>
+          <t>48092</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>43833</t>
+          <t>43819</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53369</t>
+          <t>53314</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>85127</t>
+          <t>85545</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>99133</t>
+          <t>98961</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15304</t>
+          <t>15204</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29680</t>
+          <t>27661</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19324</t>
+          <t>18984</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35021</t>
+          <t>34829</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38839</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>58665</t>
+          <t>58547</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>98942</t>
+          <t>100961</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>113318</t>
+          <t>113418</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>100634</t>
+          <t>100826</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>116331</t>
+          <t>116671</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>205612</t>
+          <t>205730</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>225438</t>
+          <t>225739</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19293</t>
+          <t>19035</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>33785</t>
+          <t>33981</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31359</t>
+          <t>30923</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48897</t>
+          <t>49095</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54439</t>
+          <t>54682</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>78695</t>
+          <t>76549</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>124119</t>
+          <t>123923</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>138611</t>
+          <t>138869</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115161</t>
+          <t>114963</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>132699</t>
+          <t>133135</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>243267</t>
+          <t>245413</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>267523</t>
+          <t>267280</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,02%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>110980</t>
+          <t>110452</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>142532</t>
+          <t>142934</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>127498</t>
+          <t>127646</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>161419</t>
+          <t>162371</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>245290</t>
+          <t>246620</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>292494</t>
+          <t>293691</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>538489</t>
+          <t>538087</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>570041</t>
+          <t>570569</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>561281</t>
+          <t>560329</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>595202</t>
+          <t>595054</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1111227</t>
+          <t>1110030</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1158431</t>
+          <t>1157101</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,43%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22011</t>
+          <t>22817</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>13223</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25704</t>
+          <t>25813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26500</t>
+          <t>26836</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43324</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>34610</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46973</t>
+          <t>45809</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39105</t>
+          <t>38996</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51642</t>
+          <t>51586</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78912</t>
+          <t>77950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>95736</t>
+          <t>95400</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,05%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>17564</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31284</t>
+          <t>31390</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18697</t>
+          <t>18140</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33308</t>
+          <t>32588</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>39225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58969</t>
+          <t>59734</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73429</t>
+          <t>73323</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87510</t>
+          <t>87149</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77851</t>
+          <t>78571</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92462</t>
+          <t>93019</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>156903</t>
+          <t>156138</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>177287</t>
+          <t>176647</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>9936</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21772</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16224</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29770</t>
+          <t>30505</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29231</t>
+          <t>29657</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46806</t>
+          <t>46858</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46406</t>
+          <t>46822</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57836</t>
+          <t>58242</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41484</t>
+          <t>40749</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>55030</t>
+          <t>54726</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>92626</t>
+          <t>92574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110201</t>
+          <t>109775</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>78,73%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13370</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25994</t>
+          <t>26281</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>9779</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22212</t>
+          <t>21825</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>25739</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44243</t>
+          <t>43712</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>51767</t>
+          <t>51480</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64391</t>
+          <t>64053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60022</t>
+          <t>60409</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72638</t>
+          <t>72455</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115752</t>
+          <t>116283</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>133142</t>
+          <t>134256</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,91%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9887</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20768</t>
+          <t>20001</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18117</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19747</t>
+          <t>19550</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34389</t>
+          <t>34051</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,56%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>23900</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34014</t>
+          <t>34543</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28635</t>
+          <t>29368</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39009</t>
+          <t>38635</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56264</t>
+          <t>56602</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70906</t>
+          <t>71103</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,43%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6438</t>
+          <t>6720</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16424</t>
+          <t>16780</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12351</t>
+          <t>12546</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24243</t>
+          <t>24740</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21885</t>
+          <t>22380</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36733</t>
+          <t>38174</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>32,84%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39561</t>
+          <t>39205</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49547</t>
+          <t>49265</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36002</t>
+          <t>35505</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47894</t>
+          <t>47699</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>79497</t>
+          <t>78056</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>94345</t>
+          <t>93850</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,74%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19593</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35308</t>
+          <t>34573</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18714</t>
+          <t>17981</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33812</t>
+          <t>33565</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42037</t>
+          <t>42345</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63797</t>
+          <t>64176</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>103410</t>
+          <t>104145</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>119125</t>
+          <t>119768</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>111927</t>
+          <t>112174</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>127025</t>
+          <t>127758</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>220660</t>
+          <t>220281</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>242420</t>
+          <t>242112</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,11%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14821</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28144</t>
+          <t>28239</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15742</t>
+          <t>15190</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29434</t>
+          <t>29310</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33195</t>
+          <t>34452</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>53680</t>
+          <t>54195</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,2%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>136564</t>
+          <t>136469</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>149887</t>
+          <t>150149</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>140382</t>
+          <t>140506</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>154074</t>
+          <t>154626</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>280844</t>
+          <t>280329</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>301329</t>
+          <t>300072</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,7%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>130280</t>
+          <t>130633</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>167322</t>
+          <t>166963</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>140344</t>
+          <t>140740</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>177591</t>
+          <t>177977</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>281654</t>
+          <t>279624</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>332147</t>
+          <t>331255</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>544069</t>
+          <t>544428</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>581111</t>
+          <t>580758</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>574417</t>
+          <t>574031</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>611664</t>
+          <t>611268</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1131252</t>
+          <t>1132144</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1181745</t>
+          <t>1183775</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,89%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>10883</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22061</t>
+          <t>21789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>12707</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>24890</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27427</t>
+          <t>27891</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44020</t>
+          <t>43599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35310</t>
+          <t>35582</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46226</t>
+          <t>46488</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>39572</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50848</t>
+          <t>51755</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77813</t>
+          <t>78234</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>94406</t>
+          <t>93942</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>77,11%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19751</t>
+          <t>20028</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34550</t>
+          <t>34491</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14498</t>
+          <t>14739</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27119</t>
+          <t>28396</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38946</t>
+          <t>38608</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58349</t>
+          <t>57871</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69397</t>
+          <t>69456</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84196</t>
+          <t>83919</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83164</t>
+          <t>81887</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95785</t>
+          <t>95544</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>155881</t>
+          <t>156359</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>175284</t>
+          <t>175622</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,98%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15739</t>
+          <t>14920</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4785</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13400</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>11811</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25708</t>
+          <t>25131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51092</t>
+          <t>51911</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61236</t>
+          <t>61052</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56521</t>
+          <t>56505</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65120</t>
+          <t>65203</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111028</t>
+          <t>111605</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124441</t>
+          <t>124925</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>91,36%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17258</t>
+          <t>17488</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>31053</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19050</t>
+          <t>18794</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33453</t>
+          <t>33163</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>39104</t>
+          <t>39825</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59107</t>
+          <t>59772</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,8%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>45983</t>
+          <t>45908</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59703</t>
+          <t>59473</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>47731</t>
+          <t>48021</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>62134</t>
+          <t>62390</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>99038</t>
+          <t>98373</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>119041</t>
+          <t>118320</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>74,82%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11225</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>9403</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>6973</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17281</t>
+          <t>17641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32067</t>
+          <t>32213</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>40158</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>37011</t>
+          <t>36947</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43928</t>
+          <t>43975</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>72507</t>
+          <t>72147</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>82784</t>
+          <t>82815</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,23%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5428</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>14364</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4247</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14766</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>11972</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>25421</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39892</t>
+          <t>39909</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>48940</t>
+          <t>48845</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42973</t>
+          <t>43563</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53492</t>
+          <t>53103</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>87089</t>
+          <t>86591</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100664</t>
+          <t>100040</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20461</t>
+          <t>21303</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6227</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16221</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>17718</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>33548</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>116913</t>
+          <t>116071</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>128292</t>
+          <t>127919</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>127851</t>
+          <t>127874</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>137774</t>
+          <t>137845</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>248113</t>
+          <t>247898</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>263566</t>
+          <t>263728</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15609</t>
+          <t>15179</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28905</t>
+          <t>28380</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18374</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33644</t>
+          <t>33170</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37259</t>
+          <t>36177</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55980</t>
+          <t>55562</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>135271</t>
+          <t>135796</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>148567</t>
+          <t>148997</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>137205</t>
+          <t>137679</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>152475</t>
+          <t>152178</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>279045</t>
+          <t>279463</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>297766</t>
+          <t>298848</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111129</t>
+          <t>111243</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>144884</t>
+          <t>143709</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>107274</t>
+          <t>108085</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>142274</t>
+          <t>141931</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>228851</t>
+          <t>227717</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>273319</t>
+          <t>273513</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>559487</t>
+          <t>560662</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>593242</t>
+          <t>593128</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>602570</t>
+          <t>602913</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>637570</t>
+          <t>636759</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1175896</t>
+          <t>1175702</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1220364</t>
+          <t>1221498</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21524</t>
+          <t>21653</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41410</t>
+          <t>41126</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16133</t>
+          <t>15658</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30199</t>
+          <t>30078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41874</t>
+          <t>41078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69051</t>
+          <t>67354</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31872</t>
+          <t>32156</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>51758</t>
+          <t>51629</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49167</t>
+          <t>49288</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63233</t>
+          <t>63708</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83597</t>
+          <t>85294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110774</t>
+          <t>111570</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>73,09%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43131</t>
+          <t>42375</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92483</t>
+          <t>90057</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37603</t>
+          <t>36365</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>59920</t>
+          <t>58381</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89002</t>
+          <t>88905</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156422</t>
+          <t>158312</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>63,09%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>30857</t>
+          <t>33283</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80209</t>
+          <t>80965</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67676</t>
+          <t>69215</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89993</t>
+          <t>91231</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>94514</t>
+          <t>92624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>161934</t>
+          <t>162031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,57%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13172</t>
+          <t>12774</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24506</t>
+          <t>23677</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14120</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26539</t>
+          <t>26698</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29843</t>
+          <t>30574</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46652</t>
+          <t>47781</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>38,09%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33762</t>
+          <t>34591</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45096</t>
+          <t>45494</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40624</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53043</t>
+          <t>52888</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78779</t>
+          <t>77650</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>95588</t>
+          <t>94857</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>75,63%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19729</t>
+          <t>18552</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18637</t>
+          <t>19677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15319</t>
+          <t>15816</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33289</t>
+          <t>33056</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>50414</t>
+          <t>51591</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>62281</t>
+          <t>62788</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59497</t>
+          <t>58457</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72619</t>
+          <t>72761</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>114989</t>
+          <t>115222</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>132959</t>
+          <t>132462</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,33%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12466</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16162</t>
+          <t>16253</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14036</t>
+          <t>13248</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25517</t>
+          <t>25655</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22047</t>
+          <t>22406</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29341</t>
+          <t>29430</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24557</t>
+          <t>24466</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34401</t>
+          <t>34376</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49715</t>
+          <t>49577</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61196</t>
+          <t>61984</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19217</t>
+          <t>19379</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>15688</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28486</t>
+          <t>28346</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34129</t>
+          <t>34025</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41796</t>
+          <t>41795</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36969</t>
+          <t>36807</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47098</t>
+          <t>47290</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73867</t>
+          <t>74007</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86977</t>
+          <t>86665</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>84,67%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22859</t>
+          <t>21780</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>38782</t>
+          <t>38520</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33681</t>
+          <t>33448</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58049</t>
+          <t>59864</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59677</t>
+          <t>60495</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>88686</t>
+          <t>88763</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85726</t>
+          <t>85988</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>101649</t>
+          <t>102728</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>97963</t>
+          <t>96148</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>122331</t>
+          <t>122564</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>191834</t>
+          <t>191757</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>220843</t>
+          <t>220025</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,43%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4587</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13177</t>
+          <t>13446</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>6769</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>17994</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13232</t>
+          <t>13944</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27259</t>
+          <t>28122</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>118442</t>
+          <t>118173</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>127149</t>
+          <t>127032</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>137343</t>
+          <t>138094</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>149202</t>
+          <t>149319</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>260448</t>
+          <t>259585</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>274475</t>
+          <t>273763</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,15%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>148523</t>
+          <t>147455</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>256457</t>
+          <t>245221</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>162543</t>
+          <t>160032</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>206332</t>
+          <t>206571</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>323800</t>
+          <t>324265</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>435188</t>
+          <t>426090</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>405384</t>
+          <t>416620</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>513318</t>
+          <t>514386</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>554933</t>
+          <t>554694</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>598722</t>
+          <t>601233</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>987918</t>
+          <t>997016</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1099306</t>
+          <t>1098841</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,21%</t>
         </is>
       </c>
     </row>
